--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BEC8AF-4410-4869-9DD4-A3FB10059935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A02CF0-1728-4510-8319-4BEDF8F97831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
-    <sheet name="История запусков" sheetId="2" r:id="rId2"/>
+    <sheet name="История запусков" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
   <si>
     <t>AQUA</t>
   </si>
@@ -245,6 +245,51 @@
   </si>
   <si>
     <t>PEG11_KUSURUKEN</t>
+  </si>
+  <si>
+    <t>PEG17_PHOENIX</t>
+  </si>
+  <si>
+    <t>UEG6_DODO</t>
+  </si>
+  <si>
+    <t>LEG1_PIN</t>
+  </si>
+  <si>
+    <t>UEG6_VULTURE</t>
+  </si>
+  <si>
+    <t>LEG1_LAKSAe</t>
+  </si>
+  <si>
+    <t>UEG4_PELICAN</t>
+  </si>
+  <si>
+    <t>LEG2_DRG</t>
+  </si>
+  <si>
+    <t>LEG1_PHOGA</t>
+  </si>
+  <si>
+    <t>UEG6_PIGEON</t>
+  </si>
+  <si>
+    <t>SEG3_FORCE</t>
+  </si>
+  <si>
+    <t>Пойдет</t>
+  </si>
+  <si>
+    <t>Коррекция</t>
+  </si>
+  <si>
+    <t>от 10</t>
+  </si>
+  <si>
+    <t>от 1 до 3</t>
+  </si>
+  <si>
+    <t>от 4 до 9</t>
   </si>
 </sst>
 </file>
@@ -267,7 +312,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,6 +355,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -332,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -343,6 +400,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -851,15 +910,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF7F82C-9520-4728-AE70-8E4FA87627D8}">
-  <dimension ref="B1:H12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2F1F35-A707-4D30-9F4E-850918EC1F71}">
+  <dimension ref="B1:P35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="7" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C1" s="3" t="s">
         <v>55</v>
       </c>
@@ -867,179 +926,485 @@
         <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>C2*10+D2*5+E2-G2-H2*5-I2*10</f>
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J35" si="0">C3*10+D3*5+E3-G3-H3*5-I3*10</f>
+        <v>-5</v>
+      </c>
+      <c r="O3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
+        <v>82</v>
+      </c>
+      <c r="P4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>60</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <f>C2*5+D2-F2-G2*5</f>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H12" si="0">C3*5+D3-F3-G3*5</f>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="0"/>
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="H7">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>6</v>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J35">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G12">
-    <sortCondition ref="B2:B12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:J22">
+    <sortCondition ref="B2:B22"/>
   </sortState>
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ED4A8701-D9DC-40D7-9041-8B0437552167}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{ED4A8701-D9DC-40D7-9041-8B0437552167}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFFB628"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>J1:J1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A02CF0-1728-4510-8319-4BEDF8F97831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C880E62D-0E5A-487B-B45C-AD0FCCAC7923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -841,7 +841,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="B21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -849,7 +849,7 @@
       </c>
     </row>
     <row r="22" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="B22" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="2" t="s">

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C880E62D-0E5A-487B-B45C-AD0FCCAC7923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF248CF8-EA25-49D3-A62D-949DA28E7AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
   <si>
     <t>AQUA</t>
   </si>
@@ -290,12 +290,42 @@
   </si>
   <si>
     <t>от 4 до 9</t>
+  </si>
+  <si>
+    <t>PEG13_DWDDCr</t>
+  </si>
+  <si>
+    <t>PEG26_UNKNOWN</t>
+  </si>
+  <si>
+    <t>PEG4_UNIVERSAL</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>Кол-во</t>
+  </si>
+  <si>
+    <t>Среднее</t>
+  </si>
+  <si>
+    <t>Прибыль</t>
+  </si>
+  <si>
+    <t>Убыток</t>
+  </si>
+  <si>
+    <t>П%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -389,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -402,6 +432,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -911,14 +943,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2F1F35-A707-4D30-9F4E-850918EC1F71}">
-  <dimension ref="B1:P35"/>
+  <dimension ref="B1:V111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
     <col min="6" max="7" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
       <c r="C1" s="3" t="s">
         <v>55</v>
       </c>
@@ -940,26 +972,67 @@
       <c r="I1" s="9" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>74</v>
       </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="J2">
         <f>C2*10+D2*5+E2-G2-H2*5-I2*10</f>
-        <v>1</v>
-      </c>
-      <c r="O2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2">
+        <f>SUM(C2:I2)</f>
+        <v>2</v>
+      </c>
+      <c r="L2" s="10">
+        <f>J2/K2</f>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <f>SUM(C2:E2)</f>
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <f>SUM(G2:I2)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="11">
+        <f>(M2/(M2+N2))*100</f>
+        <v>100</v>
+      </c>
+      <c r="U2" t="s">
         <v>83</v>
       </c>
-      <c r="P2" t="s">
+      <c r="V2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>77</v>
       </c>
@@ -967,47 +1040,113 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J35" si="0">C3*10+D3*5+E3-G3-H3*5-I3*10</f>
+        <f>C3*10+D3*5+E3-G3-H3*5-I3*10</f>
         <v>-5</v>
       </c>
-      <c r="O3" t="s">
+      <c r="K3">
+        <f t="shared" ref="K3:K35" si="0">SUM(C3:I3)</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="10">
+        <f t="shared" ref="L3:L35" si="1">J3/K3</f>
+        <v>-5</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M35" si="2">SUM(C3:E3)</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N35" si="3">SUM(G3:I3)</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="11">
+        <f t="shared" ref="O3:O35" si="4">(M3/(M3+N3))*100</f>
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
         <v>84</v>
       </c>
-      <c r="P3" t="s">
+      <c r="V3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>72</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O4" t="s">
+        <f>C4*10+D4*5+E4-G4-H4*5-I4*10</f>
+        <v>20</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" si="1"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="11">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="U4" t="s">
         <v>82</v>
       </c>
-      <c r="P4" t="s">
+      <c r="V4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>76</v>
       </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+        <f>C5*10+D5*5+E5-G5-H5*5-I5*10</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="O5" s="11">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>60</v>
       </c>
@@ -1015,363 +1154,1315 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+        <f>C6*10+D6*5+E6-G6-H6*5-I6*10</f>
+        <v>40</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="1"/>
+        <v>5.7142857142857144</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="11">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>67</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+        <f>C7*10+D7*5+E7-G7-H7*5-I7*10</f>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="O7" s="11">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>65</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
       <c r="G8">
         <v>1</v>
       </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+        <f>C8*10+D8*5+E8-G8-H8*5-I8*10</f>
+        <v>-14</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="1"/>
+        <v>-2.3333333333333335</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="O8" s="11">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <f>C9*10+D9*5+E9-G9-H9*5-I9*10</f>
+        <v>16</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="1"/>
+        <v>1.0666666666666667</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="O9" s="11">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <f>C10*10+D10*5+E10-G10-H10*5-I10*10</f>
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="11">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <f>C11*10+D11*5+E11-G11-H11*5-I11*10</f>
+        <v>-16</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="1"/>
+        <v>-3.2</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
+      <c r="O11" s="11">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <f>C12*10+D12*5+E12-G12-H12*5-I12*10</f>
+        <v>32</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L12" s="10">
+        <f t="shared" si="1"/>
+        <v>6.4</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="11">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <f>C13*10+D13*5+E13-G13-H13*5-I13*10</f>
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
+      <c r="O13" s="11">
+        <f t="shared" si="4"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <f>C14*10+D14*5+E14-G14-H14*5-I14*10</f>
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="11">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <f>C15*10+D15*5+E15-G15-H15*5-I15*10</f>
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L15" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="11">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <f>C16*10+D16*5+E16-G16-H16*5-I16*10</f>
+        <v>-1</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="O16" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <f>C17*10+D17*5+E17-G17-H17*5-I17*10</f>
+        <v>11</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" si="1"/>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="11">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <f>C18*10+D18*5+E18-G18-H18*5-I18*10</f>
+        <v>-6</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" si="1"/>
+        <v>-3</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="O18" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <f>C19*10+D19*5+E19-G19-H19*5-I19*10</f>
+        <v>-5</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="L19" s="10">
+        <f t="shared" si="1"/>
+        <v>-1.25</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="O19" s="11">
+        <f t="shared" si="4"/>
+        <v>33.333333333333329</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <f>C20*10+D20*5+E20-G20-H20*5-I20*10</f>
+        <v>-15</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="L20" s="10">
+        <f t="shared" si="1"/>
+        <v>-7.5</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="O20" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <f>C21*10+D21*5+E21-G21-H21*5-I21*10</f>
+        <v>-5</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="O21" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <f>C22*10+D22*5+E22-G22-H22*5-I22*10</f>
+        <v>-1</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="O22" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f>C23*10+D23*5+E23-G23-H23*5-I23*10</f>
+        <v>-4</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="1"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="0"/>
+      <c r="N23">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="O23" s="11">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <f>C24*10+D24*5+E24-G24-H24*5-I24*10</f>
+        <v>19</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="1"/>
+        <v>1.3571428571428572</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="0"/>
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="0"/>
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21">
+      <c r="O24" s="11">
+        <f t="shared" si="4"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <f>C25*10+D25*5+E25-G25-H25*5-I25*10</f>
+        <v>16</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="1"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="O25" s="11">
+        <f t="shared" si="4"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" ref="J3:J35" si="5">C26*10+D26*5+E26-G26-H26*5-I26*10</f>
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="10:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O32" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="10:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="10:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O34" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="11" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O36" s="11"/>
+    </row>
+    <row r="37" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O37" s="11"/>
+    </row>
+    <row r="38" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O38" s="11"/>
+    </row>
+    <row r="39" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O39" s="11"/>
+    </row>
+    <row r="40" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O40" s="11"/>
+    </row>
+    <row r="41" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O41" s="11"/>
+    </row>
+    <row r="42" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O42" s="11"/>
+    </row>
+    <row r="43" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O43" s="11"/>
+    </row>
+    <row r="44" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O44" s="11"/>
+    </row>
+    <row r="45" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O45" s="11"/>
+    </row>
+    <row r="46" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O46" s="11"/>
+    </row>
+    <row r="47" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O47" s="11"/>
+    </row>
+    <row r="48" spans="10:15" x14ac:dyDescent="0.25">
+      <c r="O48" s="11"/>
+    </row>
+    <row r="49" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O49" s="11"/>
+    </row>
+    <row r="50" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O50" s="11"/>
+    </row>
+    <row r="51" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O51" s="11"/>
+    </row>
+    <row r="52" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O52" s="11"/>
+    </row>
+    <row r="53" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O53" s="11"/>
+    </row>
+    <row r="54" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O54" s="11"/>
+    </row>
+    <row r="55" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O55" s="11"/>
+    </row>
+    <row r="56" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O56" s="11"/>
+    </row>
+    <row r="57" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O57" s="11"/>
+    </row>
+    <row r="58" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O58" s="11"/>
+    </row>
+    <row r="59" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O59" s="11"/>
+    </row>
+    <row r="60" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O60" s="11"/>
+    </row>
+    <row r="61" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O61" s="11"/>
+    </row>
+    <row r="62" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O62" s="11"/>
+    </row>
+    <row r="63" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O63" s="11"/>
+    </row>
+    <row r="64" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O64" s="11"/>
+    </row>
+    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O65" s="11"/>
+    </row>
+    <row r="66" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O66" s="11"/>
+    </row>
+    <row r="67" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O67" s="11"/>
+    </row>
+    <row r="68" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O68" s="11"/>
+    </row>
+    <row r="69" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O69" s="11"/>
+    </row>
+    <row r="70" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O70" s="11"/>
+    </row>
+    <row r="71" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O71" s="11"/>
+    </row>
+    <row r="72" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O72" s="11"/>
+    </row>
+    <row r="73" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O73" s="11"/>
+    </row>
+    <row r="74" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O74" s="11"/>
+    </row>
+    <row r="75" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O75" s="11"/>
+    </row>
+    <row r="76" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O76" s="11"/>
+    </row>
+    <row r="77" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O77" s="11"/>
+    </row>
+    <row r="78" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O78" s="11"/>
+    </row>
+    <row r="79" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O79" s="11"/>
+    </row>
+    <row r="80" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O80" s="11"/>
+    </row>
+    <row r="81" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O81" s="11"/>
+    </row>
+    <row r="82" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O82" s="11"/>
+    </row>
+    <row r="83" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O83" s="11"/>
+    </row>
+    <row r="84" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O84" s="11"/>
+    </row>
+    <row r="85" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O85" s="11"/>
+    </row>
+    <row r="86" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O86" s="11"/>
+    </row>
+    <row r="87" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O87" s="11"/>
+    </row>
+    <row r="88" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O88" s="11"/>
+    </row>
+    <row r="89" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O89" s="11"/>
+    </row>
+    <row r="90" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O90" s="11"/>
+    </row>
+    <row r="91" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O91" s="11"/>
+    </row>
+    <row r="92" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O92" s="11"/>
+    </row>
+    <row r="93" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O93" s="11"/>
+    </row>
+    <row r="94" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O94" s="11"/>
+    </row>
+    <row r="95" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O95" s="11"/>
+    </row>
+    <row r="96" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O96" s="11"/>
+    </row>
+    <row r="97" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O97" s="11"/>
+    </row>
+    <row r="98" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O98" s="11"/>
+    </row>
+    <row r="99" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O99" s="11"/>
+    </row>
+    <row r="100" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O100" s="11"/>
+    </row>
+    <row r="101" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O101" s="11"/>
+    </row>
+    <row r="102" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O102" s="11"/>
+    </row>
+    <row r="103" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O103" s="11"/>
+    </row>
+    <row r="104" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O104" s="11"/>
+    </row>
+    <row r="105" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O105" s="11"/>
+    </row>
+    <row r="106" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O106" s="11"/>
+    </row>
+    <row r="107" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O107" s="11"/>
+    </row>
+    <row r="108" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O108" s="11"/>
+    </row>
+    <row r="109" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O109" s="11"/>
+    </row>
+    <row r="110" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O110" s="11"/>
+    </row>
+    <row r="111" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O111" s="11"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:J22">
-    <sortCondition ref="B2:B22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:J25">
+    <sortCondition ref="B2:B25"/>
   </sortState>
   <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ED4A8701-D9DC-40D7-9041-8B0437552167}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EB2A134E-270B-4C6D-9190-D08FFE1547A3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L1048576">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D1DED9E8-95D3-492F-AAD6-CB2AEB1A5320}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{20F88C69-918B-40C1-841B-A5C1C0EC7E7B}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N1048576">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B5ED438B-4F7A-4DFB-80CC-570E56939A31}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:O1048576">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1380,7 +2471,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ED4A8701-D9DC-40D7-9041-8B0437552167}</x14:id>
+          <x14:id>{EF194CE7-ABEE-4D80-83A4-68A3FD9BBB53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1403,6 +2494,71 @@
           </x14:cfRule>
           <xm:sqref>J1:J1048576</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EB2A134E-270B-4C6D-9190-D08FFE1547A3}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K1:K1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D1DED9E8-95D3-492F-AAD6-CB2AEB1A5320}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFFB628"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L1:L1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{20F88C69-918B-40C1-841B-A5C1C0EC7E7B}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFFB628"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>M1:M1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B5ED438B-4F7A-4DFB-80CC-570E56939A31}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N1:N1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EF194CE7-ABEE-4D80-83A4-68A3FD9BBB53}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFFB628"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O1:O1048576</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF248CF8-EA25-49D3-A62D-949DA28E7AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33523228-8ADD-4610-9AA0-0880FD7355B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -324,7 +324,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -432,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -785,7 +785,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -999,23 +999,23 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <f>C2*10+D2*5+E2-G2-H2*5-I2*10</f>
-        <v>6</v>
+        <f t="shared" ref="J2:J25" si="0">C2*10+D2*5+E2-G2-H2*5-I2*10</f>
+        <v>7</v>
       </c>
       <c r="K2">
         <f>SUM(C2:I2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="10">
         <f>J2/K2</f>
-        <v>3</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="M2">
         <f>SUM(C2:E2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2">
         <f>SUM(G2:I2)</f>
@@ -1040,27 +1040,27 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <f>C3*10+D3*5+E3-G3-H3*5-I3*10</f>
+        <f t="shared" si="0"/>
         <v>-5</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K35" si="0">SUM(C3:I3)</f>
+        <f t="shared" ref="K3:K35" si="1">SUM(C3:I3)</f>
         <v>1</v>
       </c>
       <c r="L3" s="10">
-        <f t="shared" ref="L3:L35" si="1">J3/K3</f>
+        <f t="shared" ref="L3:L35" si="2">J3/K3</f>
         <v>-5</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M35" si="2">SUM(C3:E3)</f>
+        <f t="shared" ref="M3:M35" si="3">SUM(C3:E3)</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N35" si="3">SUM(G3:I3)</f>
+        <f t="shared" ref="N3:N35" si="4">SUM(G3:I3)</f>
         <v>1</v>
       </c>
       <c r="O3" s="11">
-        <f t="shared" ref="O3:O35" si="4">(M3/(M3+N3))*100</f>
+        <f t="shared" ref="O3:O35" si="5">(M3/(M3+N3))*100</f>
         <v>0</v>
       </c>
       <c r="U3" t="s">
@@ -1075,34 +1075,37 @@
         <v>72</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="J4">
-        <f>C4*10+D4*5+E4-G4-H4*5-I4*10</f>
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>29</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="L4" s="10">
-        <f t="shared" si="1"/>
-        <v>6.666666666666667</v>
+        <f t="shared" si="2"/>
+        <v>5.8</v>
       </c>
       <c r="M4">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="N4">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="O4" s="11">
-        <f t="shared" si="4"/>
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>80</v>
       </c>
       <c r="U4" t="s">
         <v>82</v>
@@ -1121,29 +1124,32 @@
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="J5">
-        <f>C5*10+D5*5+E5-G5-H5*5-I5*10</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>-10</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="L5" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-3.3333333333333335</v>
       </c>
       <c r="M5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N5">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="O5" s="11">
-        <f t="shared" si="4"/>
-        <v>50</v>
+        <f t="shared" si="5"/>
+        <v>33.333333333333329</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
@@ -1154,69 +1160,75 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
       <c r="J6">
-        <f>C6*10+D6*5+E6-G6-H6*5-I6*10</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="L6" s="10">
-        <f t="shared" si="1"/>
-        <v>5.7142857142857144</v>
+        <f t="shared" si="2"/>
+        <v>4.4444444444444446</v>
       </c>
       <c r="M6">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="N6">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="O6" s="11">
-        <f t="shared" si="4"/>
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>85.714285714285708</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>67</v>
       </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="J7">
-        <f>C7*10+D7*5+E7-G7-H7*5-I7*10</f>
-        <v>0</v>
-      </c>
-      <c r="K7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
       <c r="L7" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="M7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="N7">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
       <c r="O7" s="11">
-        <f t="shared" si="4"/>
-        <v>50</v>
+        <f t="shared" si="5"/>
+        <v>62.5</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.25">
@@ -1224,13 +1236,13 @@
         <v>65</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1239,28 +1251,28 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <f>C8*10+D8*5+E8-G8-H8*5-I8*10</f>
+        <f t="shared" si="0"/>
         <v>-14</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="L8" s="10">
-        <f t="shared" si="1"/>
-        <v>-2.3333333333333335</v>
+        <f t="shared" si="2"/>
+        <v>-1.75</v>
       </c>
       <c r="M8">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
       <c r="N8">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>4</v>
       </c>
       <c r="O8" s="11">
-        <f t="shared" si="4"/>
-        <v>40</v>
+        <f t="shared" si="5"/>
+        <v>42.857142857142854</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
@@ -1268,43 +1280,46 @@
         <v>69</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
       <c r="J9">
-        <f>C9*10+D9*5+E9-G9-H9*5-I9*10</f>
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="L9" s="10">
-        <f t="shared" si="1"/>
-        <v>1.0666666666666667</v>
+        <f t="shared" si="2"/>
+        <v>0.38095238095238093</v>
       </c>
       <c r="M9">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="N9">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>11</v>
       </c>
       <c r="O9" s="11">
-        <f t="shared" si="4"/>
-        <v>50</v>
+        <f t="shared" si="5"/>
+        <v>42.105263157894733</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
@@ -1314,29 +1329,32 @@
       <c r="E10">
         <v>1</v>
       </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
       <c r="J10">
-        <f>C10*10+D10*5+E10-G10-H10*5-I10*10</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N10">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="O10" s="11">
-        <f t="shared" si="4"/>
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
@@ -1346,8 +1364,11 @@
       <c r="D11">
         <v>1</v>
       </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1356,28 +1377,28 @@
         <v>2</v>
       </c>
       <c r="J11">
-        <f>C11*10+D11*5+E11-G11-H11*5-I11*10</f>
-        <v>-16</v>
+        <f t="shared" si="0"/>
+        <v>-15</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="L11" s="10">
-        <f t="shared" si="1"/>
-        <v>-3.2</v>
+        <f t="shared" si="2"/>
+        <v>-2.1428571428571428</v>
       </c>
       <c r="M11">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="N11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="O11" s="11">
-        <f t="shared" si="4"/>
-        <v>25</v>
+        <f t="shared" si="5"/>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
@@ -1385,33 +1406,33 @@
         <v>70</v>
       </c>
       <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
       <c r="J12">
-        <f>C12*10+D12*5+E12-G12-H12*5-I12*10</f>
-        <v>32</v>
+        <f t="shared" si="0"/>
+        <v>43</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="L12" s="10">
-        <f t="shared" si="1"/>
-        <v>6.4</v>
+        <f t="shared" si="2"/>
+        <v>6.1428571428571432</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="N12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O12" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
     </row>
@@ -1434,29 +1455,32 @@
       <c r="H13">
         <v>1</v>
       </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
       <c r="J13">
-        <f>C13*10+D13*5+E13-G13-H13*5-I13*10</f>
+        <f t="shared" si="0"/>
+        <v>-27</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" si="2"/>
+        <v>-2.4545454545454546</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="L13" s="10">
-        <f t="shared" si="1"/>
-        <v>0.375</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
       <c r="N13">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="O13" s="11">
-        <f t="shared" si="4"/>
-        <v>42.857142857142854</v>
+        <f t="shared" si="5"/>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
@@ -1466,29 +1490,32 @@
       <c r="E14">
         <v>1</v>
       </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
       <c r="J14">
-        <f>C14*10+D14*5+E14-G14-H14*5-I14*10</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="L14" s="10">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="O14" s="11">
-        <f t="shared" si="4"/>
-        <v>100</v>
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
@@ -1496,30 +1523,30 @@
         <v>68</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15">
-        <f>C15*10+D15*5+E15-G15-H15*5-I15*10</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="K15">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="L15" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M15">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="N15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O15" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
     </row>
@@ -1527,32 +1554,35 @@
       <c r="B16" t="s">
         <v>87</v>
       </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="J16">
-        <f>C16*10+D16*5+E16-G16-H16*5-I16*10</f>
-        <v>-1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="L16" s="10">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="N16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O16" s="11">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
@@ -1560,33 +1590,36 @@
         <v>79</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
       <c r="J17">
-        <f>C17*10+D17*5+E17-G17-H17*5-I17*10</f>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="K17">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="1"/>
-        <v>3.6666666666666665</v>
+        <f t="shared" si="2"/>
+        <v>3.2</v>
       </c>
       <c r="M17">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="N17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O17" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
     </row>
@@ -1598,30 +1631,30 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <f>C18*10+D18*5+E18-G18-H18*5-I18*10</f>
-        <v>-6</v>
+        <f t="shared" si="0"/>
+        <v>-11</v>
       </c>
       <c r="K18">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="L18" s="10">
-        <f t="shared" si="1"/>
-        <v>-3</v>
+        <f t="shared" si="2"/>
+        <v>-3.6666666666666665</v>
       </c>
       <c r="M18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N18">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="O18" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1632,6 +1665,9 @@
       <c r="D19">
         <v>1</v>
       </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
       <c r="F19">
         <v>1</v>
       </c>
@@ -1639,28 +1675,28 @@
         <v>2</v>
       </c>
       <c r="J19">
-        <f>C19*10+D19*5+E19-G19-H19*5-I19*10</f>
-        <v>-5</v>
+        <f t="shared" si="0"/>
+        <v>-4</v>
       </c>
       <c r="K19">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="L19" s="10">
-        <f t="shared" si="1"/>
-        <v>-1.25</v>
+        <f t="shared" si="2"/>
+        <v>-0.8</v>
       </c>
       <c r="M19">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="N19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="O19" s="11">
-        <f t="shared" si="4"/>
-        <v>33.333333333333329</v>
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
@@ -1674,27 +1710,27 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <f>C20*10+D20*5+E20-G20-H20*5-I20*10</f>
+        <f t="shared" si="0"/>
         <v>-15</v>
       </c>
       <c r="K20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.5</v>
       </c>
       <c r="M20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="O20" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1706,27 +1742,27 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <f>C21*10+D21*5+E21-G21-H21*5-I21*10</f>
+        <f t="shared" si="0"/>
         <v>-5</v>
       </c>
       <c r="K21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5</v>
       </c>
       <c r="M21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O21" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1740,28 +1776,31 @@
       <c r="G22">
         <v>1</v>
       </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
       <c r="J22">
-        <f>C22*10+D22*5+E22-G22-H22*5-I22*10</f>
-        <v>-1</v>
+        <f t="shared" si="0"/>
+        <v>-6</v>
       </c>
       <c r="K22">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <f t="shared" si="2"/>
+        <v>-2</v>
       </c>
       <c r="M22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N22">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="O22" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1773,43 +1812,43 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
         <v>3</v>
       </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23">
-        <v>2</v>
-      </c>
       <c r="I23">
         <v>2</v>
       </c>
       <c r="J23">
-        <f>C23*10+D23*5+E23-G23-H23*5-I23*10</f>
-        <v>-4</v>
+        <f t="shared" si="0"/>
+        <v>-3</v>
       </c>
       <c r="K23">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="1"/>
-        <v>-0.33333333333333331</v>
+        <f t="shared" si="2"/>
+        <v>-0.2</v>
       </c>
       <c r="M23">
-        <f t="shared" si="2"/>
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="N23">
-        <f t="shared" si="3"/>
-        <v>6</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="O23" s="11">
-        <f t="shared" si="4"/>
-        <v>50</v>
+        <f t="shared" si="5"/>
+        <v>53.333333333333336</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
@@ -1823,37 +1862,40 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="J24">
-        <f>C24*10+D24*5+E24-G24-H24*5-I24*10</f>
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="K24">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>18</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="1"/>
-        <v>1.3571428571428572</v>
+        <f t="shared" si="2"/>
+        <v>1.1111111111111112</v>
       </c>
       <c r="M24">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="N24">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="O24" s="11">
-        <f t="shared" si="4"/>
-        <v>71.428571428571431</v>
+        <f t="shared" si="5"/>
+        <v>70.588235294117652</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
@@ -1864,299 +1906,299 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="J25">
-        <f>C25*10+D25*5+E25-G25-H25*5-I25*10</f>
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="K25">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="1"/>
-        <v>2.6666666666666665</v>
+        <f t="shared" si="2"/>
+        <v>2.625</v>
       </c>
       <c r="M25">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="N25">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O25" s="11">
-        <f t="shared" si="4"/>
-        <v>80</v>
+        <f t="shared" si="5"/>
+        <v>83.333333333333343</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J26">
-        <f t="shared" ref="J3:J35" si="5">C26*10+D26*5+E26-G26-H26*5-I26*10</f>
+        <f t="shared" ref="J26:J35" si="6">C26*10+D26*5+E26-G26-H26*5-I26*10</f>
         <v>0</v>
       </c>
       <c r="K26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L26" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O26" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L27" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O27" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L28" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L29" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L30" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O30" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L31" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O31" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L32" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O32" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="33" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L33" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N33">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O33" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="34" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L34" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N34">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O34" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="35" spans="10:15" x14ac:dyDescent="0.25">
       <c r="J35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L35" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O35" s="11" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/__docs/trade_data.xlsx
+++ b/__docs/trade_data.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter3\__docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33523228-8ADD-4610-9AA0-0880FD7355B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A29A02-8990-4060-BEF4-23B8734519E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тикеры" sheetId="1" r:id="rId1"/>
     <sheet name="История запусков" sheetId="3" r:id="rId2"/>
+    <sheet name="Результаты" sheetId="4" r:id="rId3"/>
+    <sheet name="СумматорСегодня" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
   <si>
     <t>AQUA</t>
   </si>
@@ -317,6 +319,162 @@
   </si>
   <si>
     <t>П%</t>
+  </si>
+  <si>
+    <t>LEG2_HOTS</t>
+  </si>
+  <si>
+    <t>LEG2_LOGAN</t>
+  </si>
+  <si>
+    <t>WEG4_DOG</t>
+  </si>
+  <si>
+    <t>UEG2_GGD</t>
+  </si>
+  <si>
+    <t>PEG20_HOGGER</t>
+  </si>
+  <si>
+    <t>LEG1_OKROSHKA</t>
+  </si>
+  <si>
+    <t>LEG1_BORSCH</t>
+  </si>
+  <si>
+    <t>LEG1_PHOBO</t>
+  </si>
+  <si>
+    <t>LEG2_ALKASH</t>
+  </si>
+  <si>
+    <t>LEG2_MONSTER</t>
+  </si>
+  <si>
+    <t>WEG7_PARADOX</t>
+  </si>
+  <si>
+    <t>UEG2_GOOSE</t>
+  </si>
+  <si>
+    <t>UEG2_DUCK</t>
+  </si>
+  <si>
+    <t>UEG6_DUELDODO</t>
+  </si>
+  <si>
+    <t>UEG6_ADVENTURE</t>
+  </si>
+  <si>
+    <t>UEG6_SHERIFF</t>
+  </si>
+  <si>
+    <t>UEG7_DODO</t>
+  </si>
+  <si>
+    <t>UEG7_DUELDODO</t>
+  </si>
+  <si>
+    <t>UEG7_VULTURE</t>
+  </si>
+  <si>
+    <t>UEG7_PIGEON</t>
+  </si>
+  <si>
+    <t>UEG7_ADVENTURE</t>
+  </si>
+  <si>
+    <t>UEG7_SHERIFF</t>
+  </si>
+  <si>
+    <t>UEG8_AVENGER</t>
+  </si>
+  <si>
+    <t>PEG2_SDDCr</t>
+  </si>
+  <si>
+    <t>PEG8_DOBBY</t>
+  </si>
+  <si>
+    <t>PEG8_LOBSTER</t>
+  </si>
+  <si>
+    <t>PEG14_RWDDCr</t>
+  </si>
+  <si>
+    <t>PEG14_RANGER</t>
+  </si>
+  <si>
+    <t>PEG15_ANNA</t>
+  </si>
+  <si>
+    <t>PEG15_SILVANA</t>
+  </si>
+  <si>
+    <t>PEG18_UTER</t>
+  </si>
+  <si>
+    <t>SEG1_LITE</t>
+  </si>
+  <si>
+    <t>PEG18_REXXAR2</t>
+  </si>
+  <si>
+    <t>PEG18_UTER2</t>
+  </si>
+  <si>
+    <t>PEG18_DIABLO2</t>
+  </si>
+  <si>
+    <t>PEG18_VARIAN2</t>
+  </si>
+  <si>
+    <t>PEG18_ANDUIN</t>
+  </si>
+  <si>
+    <t>PEG19_ANUBARAK</t>
+  </si>
+  <si>
+    <t>LEG1_BIBI2</t>
+  </si>
+  <si>
+    <t>LEG1_IGOGOSHA2</t>
+  </si>
+  <si>
+    <t>LEG1_IRONANNY2</t>
+  </si>
+  <si>
+    <t>LEG1_CC2</t>
+  </si>
+  <si>
+    <t>Абс</t>
+  </si>
+  <si>
+    <t>Отн</t>
+  </si>
+  <si>
+    <t>Нейтрал</t>
+  </si>
+  <si>
+    <t>ПроцПД</t>
+  </si>
+  <si>
+    <t>Средний объем</t>
+  </si>
+  <si>
+    <t>Результаты</t>
+  </si>
+  <si>
+    <t>Новые</t>
+  </si>
+  <si>
+    <t>САП</t>
+  </si>
+  <si>
+    <t>СОП</t>
+  </si>
+  <si>
+    <t>Сумматор</t>
   </si>
 </sst>
 </file>
@@ -342,7 +500,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +555,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -419,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -434,6 +598,12 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2605,4 +2775,6384 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8FFDFC-F0D8-484F-BD9F-73CE26658A10}">
+  <dimension ref="A1:Y77"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>IFERROR((F2/E2)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="15">
+        <f>IFERROR(C2/E2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="15">
+        <f>IFERROR(D2/E2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>C2+T2</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>D2+U2</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>E2+V2</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>F2+W2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>G2+X2</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>H2+Y2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <f t="shared" ref="I3:I66" si="0">IFERROR((F3/E3)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="15">
+        <f t="shared" ref="J3:J66" si="1">IFERROR(C3/E3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" ref="K3:K66" si="2">IFERROR(D3/E3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M66" si="3">C3+T3</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>D3+U3</f>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f>E3+V3</f>
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <f>F3+W3</f>
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f>G3+X3</f>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <f>H3+Y3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>D4+U4</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f>E4+V4</f>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f>F4+W4</f>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f>G4+X4</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f>H4+Y4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f>D5+U5</f>
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <f>E5+V5</f>
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <f>F5+W5</f>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f>G5+X5</f>
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <f>H5+Y5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>D6+U6</f>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f>E6+V6</f>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f>F6+W6</f>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f>G6+X6</f>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f>H6+Y6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1.2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" si="2"/>
+        <v>0.39999999999999997</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="N7">
+        <f>D7+U7</f>
+        <v>1.2</v>
+      </c>
+      <c r="O7">
+        <f>E7+V7</f>
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <f>F7+W7</f>
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <f>G7+X7</f>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f>H7+Y7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f>D8+U8</f>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f>E8+V8</f>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f>F8+W8</f>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f>G8+X8</f>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f>H8+Y8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <f>D9+U9</f>
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <f>E9+V9</f>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f>F9+W9</f>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f>G9+X9</f>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f>H9+Y9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>-6</v>
+      </c>
+      <c r="D10">
+        <v>-1.2</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="1"/>
+        <v>-6</v>
+      </c>
+      <c r="K10" s="15">
+        <f t="shared" si="2"/>
+        <v>-1.2</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="N10">
+        <f>D10+U10</f>
+        <v>-1.2</v>
+      </c>
+      <c r="O10">
+        <f>E10+V10</f>
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <f>F10+W10</f>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f>G10+X10</f>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f>H10+Y10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11">
+        <v>35</v>
+      </c>
+      <c r="D11">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="K11" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="N11">
+        <f>D11+U11</f>
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="O11">
+        <f>E11+V11</f>
+        <v>5</v>
+      </c>
+      <c r="P11">
+        <f>F11+W11</f>
+        <v>4</v>
+      </c>
+      <c r="Q11">
+        <f>G11+X11</f>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f>H11+Y11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <f>D12+U12</f>
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <f>E12+V12</f>
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <f>F12+W12</f>
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <f>G12+X12</f>
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <f>H12+Y12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13">
+        <v>-12</v>
+      </c>
+      <c r="D13">
+        <v>-2.4</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13" s="11">
+        <f t="shared" si="0"/>
+        <v>33.333333333333329</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="1"/>
+        <v>-4</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="2"/>
+        <v>-0.79999999999999993</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="3"/>
+        <v>-12</v>
+      </c>
+      <c r="N13">
+        <f>D13+U13</f>
+        <v>-2.4</v>
+      </c>
+      <c r="O13">
+        <f>E13+V13</f>
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <f>F13+W13</f>
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <f>G13+X13</f>
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <f>H13+Y13</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14">
+        <v>40</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" s="11">
+        <f t="shared" si="0"/>
+        <v>71.428571428571431</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="1"/>
+        <v>5.7142857142857144</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1428571428571428</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="N14">
+        <f>D14+U14</f>
+        <v>8</v>
+      </c>
+      <c r="O14">
+        <f>E14+V14</f>
+        <v>7</v>
+      </c>
+      <c r="P14">
+        <f>F14+W14</f>
+        <v>5</v>
+      </c>
+      <c r="Q14">
+        <f>G14+X14</f>
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <f>H14+Y14</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>1.2</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15" s="11">
+        <f t="shared" si="0"/>
+        <v>62.5</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.15</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="N15">
+        <f>D15+U15</f>
+        <v>1.2</v>
+      </c>
+      <c r="O15">
+        <f>E15+V15</f>
+        <v>8</v>
+      </c>
+      <c r="P15">
+        <f>F15+W15</f>
+        <v>5</v>
+      </c>
+      <c r="Q15">
+        <f>G15+X15</f>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <f>H15+Y15</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <f>D16+U16</f>
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <f>E16+V16</f>
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <f>F16+W16</f>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f>G16+X16</f>
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <f>H16+Y16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f>D17+U17</f>
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <f>E17+V17</f>
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <f>F17+W17</f>
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <f>G17+X17</f>
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <f>H17+Y17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18">
+        <v>-11.9</v>
+      </c>
+      <c r="D18">
+        <v>-2.3800000000000003</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18" s="11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="1"/>
+        <v>-1.4875</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="2"/>
+        <v>-0.29750000000000004</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="3"/>
+        <v>-11.9</v>
+      </c>
+      <c r="N18">
+        <f t="shared" ref="N18:N67" si="4">D18+U18</f>
+        <v>-2.3800000000000003</v>
+      </c>
+      <c r="O18">
+        <f t="shared" ref="O18:O67" si="5">E18+V18</f>
+        <v>8</v>
+      </c>
+      <c r="P18">
+        <f t="shared" ref="P18:P67" si="6">F18+W18</f>
+        <v>4</v>
+      </c>
+      <c r="Q18">
+        <f>G18+X18</f>
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <f>H18+Y18</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <f>G19+X19</f>
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <f>H19+Y19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="D20">
+        <v>-2.0000000000000285E-2</v>
+      </c>
+      <c r="E20">
+        <v>21</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>12</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" si="0"/>
+        <v>38.095238095238095</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" si="1"/>
+        <v>-4.76190476190483E-3</v>
+      </c>
+      <c r="K20" s="15">
+        <f t="shared" si="2"/>
+        <v>-9.5238095238096593E-4</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="3"/>
+        <v>-0.10000000000000142</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="4"/>
+        <v>-2.0000000000000285E-2</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="Q20">
+        <f>G20+X20</f>
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <f>H20+Y20</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0.2</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="J21" s="15">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="15">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <f>G21+X21</f>
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <f>H21+Y21</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f>G22+X22</f>
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <f>H22+Y22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" si="1"/>
+        <v>1.75</v>
+      </c>
+      <c r="K23" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="4"/>
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="Q23">
+        <f>G23+X23</f>
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <f>H23+Y23</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <f>G24+X24</f>
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <f>H24+Y24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <f>G25+X25</f>
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <f>H25+Y25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <f>G26+X26</f>
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <f>H26+Y26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27">
+        <v>47</v>
+      </c>
+      <c r="D27">
+        <v>9.4</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="1"/>
+        <v>7.833333333333333</v>
+      </c>
+      <c r="K27" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5666666666666667</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="4"/>
+        <v>9.4</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="Q27">
+        <f>G27+X27</f>
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <f>H27+Y27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <f>G28+X28</f>
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <f>H28+Y28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29">
+        <v>-40</v>
+      </c>
+      <c r="D29">
+        <v>-8</v>
+      </c>
+      <c r="E29">
+        <v>11</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="I29" s="11">
+        <f t="shared" si="0"/>
+        <v>27.27272727272727</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="1"/>
+        <v>-3.6363636363636362</v>
+      </c>
+      <c r="K29" s="15">
+        <f t="shared" si="2"/>
+        <v>-0.72727272727272729</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="3"/>
+        <v>-40</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="4"/>
+        <v>-8</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="Q29">
+        <f>G29+X29</f>
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <f>H29+Y29</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <f>G30+X30</f>
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <f>H30+Y30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <f>G31+X31</f>
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <f>H31+Y31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <f>G32+X32</f>
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <f>H32+Y32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <f>G33+X33</f>
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <f>H33+Y33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <f>G34+X34</f>
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <f>H34+Y34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <f>G35+X35</f>
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <f>H35+Y35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <f>G36+X36</f>
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <f>H36+Y36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <f>G37+X37</f>
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <f>H37+Y37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" s="11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="P38">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Q38">
+        <f>G38+X38</f>
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <f>H38+Y38</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>1.2</v>
+      </c>
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="K39" s="15">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="4"/>
+        <v>1.2</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="P39">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="Q39">
+        <f>G39+X39</f>
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <f>H39+Y39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40">
+        <v>-1</v>
+      </c>
+      <c r="D40">
+        <v>-0.2</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" s="11">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="K40" s="15">
+        <f t="shared" si="2"/>
+        <v>-0.1</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="4"/>
+        <v>-0.2</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <f>G40+X40</f>
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <f>H40+Y40</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <f>G41+X41</f>
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <f>H41+Y41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <f>G42+X42</f>
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <f>H42+Y42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <f>G43+X43</f>
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <f>H43+Y43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44">
+        <v>15</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44" s="11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K44" s="15">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="Q44">
+        <f>G44+X44</f>
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <f>H44+Y44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <f>G45+X45</f>
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <f>H45+Y45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <f>G46+X46</f>
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <f>H46+Y46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <f>G47+X47</f>
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <f>H47+Y47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48">
+        <v>-12</v>
+      </c>
+      <c r="D48">
+        <v>-2.4</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="15">
+        <f t="shared" si="1"/>
+        <v>-6</v>
+      </c>
+      <c r="K48" s="15">
+        <f t="shared" si="2"/>
+        <v>-1.2</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="3"/>
+        <v>-12</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="4"/>
+        <v>-2.4</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <f>G48+X48</f>
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <f>H48+Y48</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49">
+        <v>-2.9000000000000004</v>
+      </c>
+      <c r="D49">
+        <v>-0.58000000000000007</v>
+      </c>
+      <c r="E49">
+        <v>5</v>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>2</v>
+      </c>
+      <c r="I49" s="11">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="J49" s="15">
+        <f t="shared" si="1"/>
+        <v>-0.58000000000000007</v>
+      </c>
+      <c r="K49" s="15">
+        <f t="shared" si="2"/>
+        <v>-0.11600000000000002</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="3"/>
+        <v>-2.9000000000000004</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="4"/>
+        <v>-0.58000000000000007</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="Q49">
+        <f>G49+X49</f>
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <f>H49+Y49</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <f>G50+X50</f>
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <f>H50+Y50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <f>G51+X51</f>
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <f>H51+Y51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <f>G52+X52</f>
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <f>H52+Y52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <f>G53+X53</f>
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <f>H53+Y53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <f>G54+X54</f>
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <f>H54+Y54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55">
+        <v>-6.1</v>
+      </c>
+      <c r="D55">
+        <v>-1.22</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+      <c r="I55" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="15">
+        <f t="shared" si="1"/>
+        <v>-2.0333333333333332</v>
+      </c>
+      <c r="K55" s="15">
+        <f t="shared" si="2"/>
+        <v>-0.40666666666666668</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="3"/>
+        <v>-6.1</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="4"/>
+        <v>-1.22</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <f>G55+X55</f>
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <f>H55+Y55</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <f>G56+X56</f>
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <f>H56+Y56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <f>G57+X57</f>
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <f>H57+Y57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <f>G58+X58</f>
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <f>H58+Y58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <f>G59+X59</f>
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <f>H59+Y59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <f>G60+X60</f>
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <f>H60+Y60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>112</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <f>G61+X61</f>
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <f>H61+Y61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <f>G62+X62</f>
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <f>H62+Y62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>13</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>6</v>
+      </c>
+      <c r="I63" s="11">
+        <f t="shared" si="0"/>
+        <v>53.846153846153847</v>
+      </c>
+      <c r="J63" s="15">
+        <f t="shared" si="1"/>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="K63" s="15">
+        <f t="shared" si="2"/>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="P63">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="Q63">
+        <f>G63+X63</f>
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <f>H63+Y63</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>61</v>
+      </c>
+      <c r="C64">
+        <v>29.1</v>
+      </c>
+      <c r="D64">
+        <v>5.82</v>
+      </c>
+      <c r="E64">
+        <v>18</v>
+      </c>
+      <c r="F64">
+        <v>13</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64" s="11">
+        <f t="shared" si="0"/>
+        <v>72.222222222222214</v>
+      </c>
+      <c r="J64" s="15">
+        <f t="shared" si="1"/>
+        <v>1.6166666666666667</v>
+      </c>
+      <c r="K64" s="15">
+        <f t="shared" si="2"/>
+        <v>0.32333333333333336</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="3"/>
+        <v>29.1</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="4"/>
+        <v>5.82</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="P64">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="Q64">
+        <f>G64+X64</f>
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <f>H64+Y64</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <f>G65+X65</f>
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <f>H65+Y65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66">
+        <v>22.9</v>
+      </c>
+      <c r="D66">
+        <v>4.58</v>
+      </c>
+      <c r="E66">
+        <v>8</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+      <c r="I66" s="11">
+        <f t="shared" si="0"/>
+        <v>62.5</v>
+      </c>
+      <c r="J66" s="15">
+        <f t="shared" si="1"/>
+        <v>2.8624999999999998</v>
+      </c>
+      <c r="K66" s="15">
+        <f t="shared" si="2"/>
+        <v>0.57250000000000001</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="3"/>
+        <v>22.9</v>
+      </c>
+      <c r="N66">
+        <f t="shared" si="4"/>
+        <v>4.58</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="P66">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="Q66">
+        <f>G66+X66</f>
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <f>H66+Y66</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" s="11">
+        <f t="shared" ref="I67" si="7">IFERROR((F67/E67)*100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="15">
+        <f t="shared" ref="J67" si="8">IFERROR(C67/E67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K67" s="15">
+        <f t="shared" ref="K67" si="9">IFERROR(D67/E67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <f t="shared" ref="M67" si="10">C67+T67</f>
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <f>G67+X67</f>
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <f>H67+Y67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B75" s="12"/>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B76" s="12"/>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B77" s="12"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B106">
+    <sortCondition ref="B1:B106"/>
+  </sortState>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7D10D13C-C571-4B59-93B5-12E7A59A1CCD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D3CC7566-39D3-442D-B264-09F8FB894D7E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D11EAE19-2FE0-487D-807E-F3158426B75C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DEA1496F-97D6-4457-8BC6-5686A3A3E290}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7EED29B2-BD73-4FCE-A7F4-C513664D4836}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{73528973-DA01-41C1-B487-0DE1464CE7F4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{19BA1BDB-A63C-42B1-96C9-B439C2E4A76C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{10927AF3-62C6-4960-B1F7-114136005372}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2C258912-4D56-494D-906F-21CEDB1D53A1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7D10D13C-C571-4B59-93B5-12E7A59A1CCD}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D3CC7566-39D3-442D-B264-09F8FB894D7E}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D1:D1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D11EAE19-2FE0-487D-807E-F3158426B75C}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DEA1496F-97D6-4457-8BC6-5686A3A3E290}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F1:F1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7EED29B2-BD73-4FCE-A7F4-C513664D4836}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G1:G1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{73528973-DA01-41C1-B487-0DE1464CE7F4}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{19BA1BDB-A63C-42B1-96C9-B439C2E4A76C}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I1:I1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{10927AF3-62C6-4960-B1F7-114136005372}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>J1:J1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2C258912-4D56-494D-906F-21CEDB1D53A1}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K1:K1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A53AFF8-0615-4AA5-B49F-FDA402810813}">
+  <dimension ref="A1:AB68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="8" max="28" width="9.140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3">
+        <f>SUM(H3:AB3)</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>(B3/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>COUNTA(H3:AB3)</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>COUNTIF(H3:AB3, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>COUNTIF(H3:AB3, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>COUNTIF(H3:AB3, "&lt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:B67" si="0">SUM(H4:AB4)</f>
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C67" si="1">(B4/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D67" si="2">COUNTA(H4:AB4)</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E67" si="3">COUNTIF(H4:AB4, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F67" si="4">COUNTIF(H4:AB4, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G67" si="5">COUNTIF(H4:AB4, "&lt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>104</v>
+      </c>
+      <c r="B68">
+        <f t="shared" ref="B68" si="6">SUM(H68:AB68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <f t="shared" ref="C68" si="7">(B68/$C$1)*100</f>
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <f t="shared" ref="D68" si="8">COUNTA(H68:AB68)</f>
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <f t="shared" ref="E68" si="9">COUNTIF(H68:AB68, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <f t="shared" ref="F68" si="10">COUNTIF(H68:AB68, "=0")</f>
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <f t="shared" ref="G68" si="11">COUNTIF(H68:AB68, "&lt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>